--- a/.docs/quest_tracking.xlsx
+++ b/.docs/quest_tracking.xlsx
@@ -401,7 +401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="5" min="3" max="3"/>
@@ -478,61 +478,448 @@
       </c>
     </row>
     <row r="2" ht="48.5" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>the-boundary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>The Boundary</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hub__westside_corner</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>victory
+neutral
+defeat</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Someone's been running product two blocks into Kings territory from the Flats side. The council wants it stopped quietly. They're asking you.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>victory: the-boundary__done
+neutral: the-boundary__messy
+defeat: the-boundary__burned</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="41.75" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>the-regular</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>The Regular</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hub__corkys</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>victory
+neutral
+defeat</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Danny Kowalski hasn't been in for two weeks. Tuesday, Thursday, every week for eleven years, and then nothing. Sal's not asking you to do anything about it. He's just saying it.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>victory: the-regular__done
+neutral: the-regular__scared-off
+defeat: the-regular__beaten</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45.5" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Strip Job</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hub__the_strip</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>victory
+neutral
+defeat</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>the-tab</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>There's an electronics shop two blocks down from the corner. You've walked past it three times this week without meaning to. Tonight feels like the night.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>victory: the-strip-job__done
+neutral: the-strip-job__complications
+defeat: the-strip-job__burned</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="43.25" customHeight="1" s="6">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the-tab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Tab</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hub__corkys</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>the-strip-job (any ending)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>victory
+neutral (x2)
+defeat</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>A guy ran up a tab he couldn't cover and left a flash drive behind the bar. Now two different people are asking about him. Sal wants to know if he needs to worry.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>victory: the-tab__clean
+neutral: the-tab__blues
+neutral: the-tab__buccos
+defeat: the-tab__burned</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The Tail</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hub__the_strip</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>victory
+neutral (x2)
+defeat</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Burner number, no name. Someone's watching a Strip regular and the caller wants to know who hired them. Then they want them gone.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>victory: the-tail__clean-exit
+neutral: the-tail__loose-end
+neutral: the-tail__messy-exit
+defeat: the-tail__burned</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The Witness</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hub__westside_corner</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>the-tail (any ending)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>victory
+neutral (x2)
+defeat</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>A Kings soldier named Calvin has been missing for four days. His crew thinks he's being leaned on. They want someone outside the Kings to find him before it becomes a loyalty quest...</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>neutral: the-witness__clean-return
+neutral: the-witness__deon-knows
+victory: the-witness__council
+defeat: the-witness__sitting-on-it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>The Call</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>intro</t>
         </is>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>hub__apartment</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>victory (x2)
 defeat</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>Introduces Vickie and Terrell. Two victory paths: talked out or fought.</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Your sister reached out. First time in three years. She needs something taken care of. Family's family.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>victory: the-call__done-clean
 victory: the-call__done-rough
@@ -540,189 +927,249 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="41.75" customHeight="1" s="6">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>crossing-lines</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Crossing Lines</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hub__apartment</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>the-morris-job (any ending)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>victory</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Morris has a delivery that touches more parts of the city than it should. That’s either a mistake or the point.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>victory: crossing-lines__ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>The Morris Job</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>intro</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>hub__apartment</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>the-call (any ending)</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>victory
 neutral (x2)</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>corkys, crossing-lines</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Someone called Morris has a package that needs moving across the Flats. Simple job. First one usually is.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>victory: the-morris-job__clean-delivery
+neutral: the-morris-job__hot-delivery
+neutral: the-morris-job__clocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>corkys</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>Introduces Morris and Dutch's operation. First courier job. Morris gained at entrance.</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>victory: the-morris-job__clean-delivery
-neutral: the-morris-job__clocked
-neutral: the-morris-job__hot-delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45.5" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Corky's</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>intro</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>hub__apartment</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>the-morris-job (any ending)</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>victory
 neutral
 defeat</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>Introduces Sal. Player pressures a civilian. Three approach paths.</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Dutch wants his dealers back in a bar called Corky's. The owner pushed back. You're the push.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>victory: corkys__done-dealers-in
-neutral: corkys__done-sal-caved
-defeat: corkys__done-sal-holds</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="43.25" customHeight="1" s="6">
-      <c r="A5" s="9" t="inlineStr">
+defeat: corkys__done-sal-holds
+neutral: corkys__done-sal-caved</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>The Ride</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>intro</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>hub__apartment</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>corkys (any ending)</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>victory (x2)
 defeat</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>Introduces Darius. Key choice: report to Dutch or stay quiet. Opens Kings cold-war thread.</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Morris has a courier job. Pick up a package, deliver it across the Flats. Simple work. It stops being simple at the handoff.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>victory: the-ride__done-straight
 victory: the-ride__done-covered
@@ -743,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10.06" customWidth="1" style="5" min="1" max="1"/>
@@ -799,368 +1246,636 @@
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>the-boundary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>the-regular</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.75" customHeight="1" s="6">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the-tab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" s="6">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.75" customHeight="1" s="6">
+      <c r="A8" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>victory (talked out)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D8" t="n">
         <v>15</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>sister</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="6">
-      <c r="A3" s="9" t="inlineStr">
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="6">
+      <c r="A9" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>victory (fought)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C9" t="n">
         <v>150</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E9" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>brass_knuckles, zonk_smoked</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>sister</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr"/>
-    </row>
-    <row r="4" ht="21.75" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="6">
+      <c r="A10" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>defeat</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C10" t="n">
         <v>-25</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D10" t="n">
         <v>-5</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E10" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>zonk_smoked</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="6">
-      <c r="A5" s="9" t="inlineStr">
+    </row>
+    <row r="11" ht="21.75" customHeight="1" s="6">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>crossing-lines</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.75" customHeight="1" s="6">
+      <c r="A12" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>victory</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C12" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D12" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>switchblade, zonk_smoked</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>morris</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>harlan-street-crew +10</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>the-morris-job</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>neutral (clocked)</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>175</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>zonk_smoked</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>morris</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>harlan-street-crew +5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="6">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>the-morris-job</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>neutral (hot delivery)</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>zonk_smoked</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>morris</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>harlan-street-crew +3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="6">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>victory (intimidated)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="6">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>victory (leveraged)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="6">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" s="6">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>defeat</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9" t="inlineStr"/>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" s="6">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>the-ride</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>victory (straight)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>350</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>the-ride</t>
+          <t>the-morris-job</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>victory (covered)</t>
+          <t>neutral (clocked)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>zonk_smoked</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>morris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>harlan-street-crew +5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>the-morris-job</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>neutral (hot delivery)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>zonk_smoked</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>morris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>harlan-street-crew +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>victory (intimidated)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>victory (leveraged)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>200</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>defeat</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>victory (straight)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>350</v>
+      </c>
+      <c r="D19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>the-ride</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>victory (covered)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>300</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>the-ride</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>defeat</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D21" t="n">
         <v>-20</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E21" t="n">
         <v>10</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1175,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22.4" customWidth="1" style="5" min="1" max="1"/>
@@ -1213,335 +1928,625 @@
       </c>
     </row>
     <row r="2" ht="47" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>corkys_read_room</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>corkys__read-the-room / Approach Sal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Flag set via choice in corkys__read-the-room</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>corkys_dealers_in</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>corkys__done-dealers-in / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Flag set via choice in corkys__done-dealers-in</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>corkys_sal_holds</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>corkys__done-sal-holds / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Flag set via choice in corkys__done-sal-holds</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" s="6">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>corkys_sal_caved</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>corkys__done-sal-caved / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Flag set via choice in corkys__done-sal-caved</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>the_call_talked_out</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>the-call__done-clean (hub return)</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>Player resolved Terrell without combat</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>the-call__done-clean / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-call__done-clean</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="6">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="7" ht="30" customHeight="1" s="6">
+      <c r="A7" t="inlineStr">
         <is>
           <t>the_call_fought_out</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>the-call__done-rough (hub return)</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Player fought and won against Terrell</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>the-call__done-rough / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-call__done-rough</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="8" ht="30" customHeight="1" s="6">
+      <c r="A8" t="inlineStr">
         <is>
           <t>the_call_lost</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>the-call__beaten (hub return)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Player lost the fight with Terrell</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>the-call__beaten / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-call__beaten</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="6">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="6">
+      <c r="A9" t="inlineStr">
         <is>
           <t>morris_job_clean</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>the-morris-job__clean-delivery (hub return)</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Clean delivery, no police contact</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>the-morris-job__clean-delivery / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-morris-job__clean-delivery</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="6">
+      <c r="A10" t="inlineStr">
         <is>
           <t>morris_job_hot</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>the-morris-job__hot-delivery or __clocked (hub return)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Delivery logged by Blues, both neutral endings</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>the-morris-job__hot-delivery / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-morris-job__hot-delivery</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="6">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>corkys_dealers_in</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>corkys__done-dealers-in (hub return)</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Dealers back in, victory ending</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+    <row r="11" ht="44" customHeight="1" s="6">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>morris_job_hot</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>the-morris-job</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>the-morris-job__clocked / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-morris-job__clocked</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="6">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>corkys_sal_holds</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>corkys__done-sal-holds (hub return)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Counter-offer built, Dutch rejected it, defeat ending</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+    <row r="12" ht="47" customHeight="1" s="6">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>the_ride_straight</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>the-ride</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>the-ride__done-straight / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-ride__done-straight</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="6">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>corkys_sal_caved</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>corkys__done-sal-caved (hub return)</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Sal held firm, Dutch handled it, neutral ending</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="6">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>the_ride_covered</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>the-ride</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>the-ride__done-covered / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-ride__done-covered</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="6">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>corkys_read_room</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>corkys__read-the-room (approach choice)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Player observed the bar, gates leverage choice</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>corkys__sal-face-to-face (leverage option)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1" s="6">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>the_ride_straight</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+    <row r="14" ht="30" customHeight="1" s="6">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>the_ride_lost</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>the-ride__done-straight (hub return)</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Told Morris everything about Darius</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>the-ride__done-lost / Back to the apartment</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-ride__done-lost</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="47" customHeight="1" s="6">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>the_ride_covered</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>the-ride</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>the-ride__done-covered (hub return)</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Kept Darius quiet</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>strip_job_cased</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>the-strip-job__the-corner / Watch it a while longer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-strip-job__the-corner</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="6">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>the_ride_lost</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>the-ride</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>the-ride__done-lost (hub return)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Package lost, Dutch owed a debt in work</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>strip_job_witness</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>the-strip-job__the-back-room / Tell him to forget he saw you</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-strip-job__the-back-room</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Future gating TBD</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="6">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>strip_job_witness</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>the-strip-job__the-back-room / Take his phone first</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-strip-job__the-back-room</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>strip_job_witness_tied</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>the-strip-job__the-back-room / Zip tie him to the shelf</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-strip-job__the-back-room</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tail_watcher_tied</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>the-tail__what-to-do / Zip tie him to the steering wheel and walk</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-tail__what-to-do</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tail_watcher_loose</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>the-tail__what-to-do / Tell him to drive and not come back</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-tail__what-to-do</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>witness_calvin_silent</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>the-witness__the-decision / Tell Calvin to say he saw nothing, send him back clean</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-witness__the-decision</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>witness_deon_told</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>the-witness__the-decision / Tell Deon exactly what Calvin saw</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-witness__the-decision</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>witness_council_told</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>the-witness__the-decision / Take it to the Kings council directly</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-witness__the-decision</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>witness_held</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>the-witness__the-decision / Keep the information yourself, send Calvin back with nothing</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Flag set via choice in the-witness__the-decision</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Future gating TBD</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1556,7 +2561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10.06" customWidth="1" style="5" min="1" max="1"/>
@@ -1588,66 +2593,132 @@
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>corkys</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quest_completed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Any ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>crossing-lines</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>the-morris-job</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quest_completed</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Any ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>the-morris-job</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>quest_completed</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Any ending</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="21.75" customHeight="1" s="6">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the-ride</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>corkys</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>the-morris-job</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>quest_completed</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Any ending</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="21.75" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>the-ride</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>corkys</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>the-tab</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>quest_completed</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Any ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quest_completed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Any ending</t>
         </is>
@@ -1666,7 +2737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12.94" customWidth="1" style="5" min="2" max="2"/>
@@ -1707,116 +2778,356 @@
       </c>
     </row>
     <row r="2" ht="21.75" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>the-boundary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>the-regular</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.75" customHeight="1" s="6">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the-tab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" s="6">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>crossing-lines</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr"/>
-    </row>
-    <row r="4" ht="21.75" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>corkys</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="6">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1831,7 +3142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10.06" customWidth="1" style="5" min="1" max="1"/>
@@ -1863,264 +3174,418 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" s="6">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>the-boundary</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" s="6">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>the-regular</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="6">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>the-strip-job</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="47.75" customHeight="1" s="6">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the-tab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" s="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>the-tail</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="41.75" customHeight="1" s="6">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>the-witness</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40.25" customHeight="1" s="6">
+      <c r="A8" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Vickie (sister)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Contact gained</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Sister gained on both victory paths</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="6">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="9" ht="30" customHeight="1" s="6">
+      <c r="A9" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Terrell</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Character introduced</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Low-level enforcer, may recur</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="10" ht="30" customHeight="1" s="6">
+      <c r="A10" t="inlineStr">
         <is>
           <t>the-call</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Westside Kings</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Faction awareness</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Player acts on Kings-adjacent turf for first time</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="47.75" customHeight="1" s="6">
-      <c r="A5" s="9" t="inlineStr">
+    <row r="11" ht="30" customHeight="1" s="6">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>crossing-lines</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Derived from YAML - pending narrative curation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="6">
+      <c r="A12" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Morris</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Contact gained</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Morris gained at quest entrance (first scene arrival)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="13" ht="30" customHeight="1" s="6">
+      <c r="A13" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Dutch</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Reputation established</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Dutch learns player's name on clean victory; monitors on neutral paths</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="41.75" customHeight="1" s="6">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>the-morris-job</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Harlan Street Crew</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Standing</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>+10 victory, +5 clocked, +3 hot delivery</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40.25" customHeight="1" s="6">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>corkys</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Sal</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Character introduced</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Sal introduced, potential future hub owner depending on arc resolution</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="6">
-      <c r="A9" s="9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>corkys</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Corky's</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Location status</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Dealers back in (victory/neutral) or Dutch handles it himself (defeat)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="6">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>corkys</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Dutch</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Reputation</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Victory builds standing; defeat signals player's limits to Morris</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="6">
-      <c r="A11" s="9" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Darius</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Character introduced</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Operator working independently of his crew, recurring thread</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="6">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Dutch / Morris</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Information state</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Straight: Dutch knows Darius's name and message. Covered: he doesn't.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="6">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>the-ride</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Westside Kings</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Tension raised</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Darius operating without sanction, first visible fracture in BSB/Kings boundary</t>
         </is>
